--- a/data/nzd0396/nzd0396.xlsx
+++ b/data/nzd0396/nzd0396.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N428"/>
+  <dimension ref="A1:N429"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20986,6 +20986,54 @@
       <c r="N428" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:07:59+00:00</t>
+        </is>
+      </c>
+      <c r="B429" t="n">
+        <v>345.99</v>
+      </c>
+      <c r="C429" t="n">
+        <v>332.45</v>
+      </c>
+      <c r="D429" t="n">
+        <v>334.73</v>
+      </c>
+      <c r="E429" t="n">
+        <v>338.14</v>
+      </c>
+      <c r="F429" t="n">
+        <v>344.25</v>
+      </c>
+      <c r="G429" t="n">
+        <v>344.44</v>
+      </c>
+      <c r="H429" t="n">
+        <v>345.44</v>
+      </c>
+      <c r="I429" t="n">
+        <v>345.39</v>
+      </c>
+      <c r="J429" t="n">
+        <v>341.7</v>
+      </c>
+      <c r="K429" t="n">
+        <v>336.96</v>
+      </c>
+      <c r="L429" t="n">
+        <v>334.96</v>
+      </c>
+      <c r="M429" t="n">
+        <v>334.71</v>
+      </c>
+      <c r="N429" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -21000,7 +21048,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B435"/>
+  <dimension ref="A1:B436"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25353,6 +25401,16 @@
       </c>
       <c r="B435" t="n">
         <v>-0.58</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B436" t="n">
+        <v>0.17</v>
       </c>
     </row>
   </sheetData>
@@ -25521,28 +25579,28 @@
         <v>0.0562</v>
       </c>
       <c r="I2" t="n">
-        <v>0.769006957574666</v>
+        <v>0.7696257866248658</v>
       </c>
       <c r="J2" t="n">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="K2" t="n">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4032268424679993</v>
+        <v>0.404755429210354</v>
       </c>
       <c r="M2" t="n">
-        <v>5.740781812081502</v>
+        <v>5.729432781209129</v>
       </c>
       <c r="N2" t="n">
-        <v>50.0197264458408</v>
+        <v>49.9073890712255</v>
       </c>
       <c r="O2" t="n">
-        <v>7.072462544675708</v>
+        <v>7.064516195127979</v>
       </c>
       <c r="P2" t="n">
-        <v>324.3100772025853</v>
+        <v>324.3037425042418</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25599,28 +25657,28 @@
         <v>0.0827</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6380436698446048</v>
+        <v>0.638641664100378</v>
       </c>
       <c r="J3" t="n">
+        <v>428</v>
+      </c>
+      <c r="K3" t="n">
         <v>427</v>
       </c>
-      <c r="K3" t="n">
-        <v>426</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.4488331151760466</v>
+        <v>0.4504593341204336</v>
       </c>
       <c r="M3" t="n">
-        <v>4.217852296942076</v>
+        <v>4.210345901212378</v>
       </c>
       <c r="N3" t="n">
-        <v>28.35554730507026</v>
+        <v>28.29332679876951</v>
       </c>
       <c r="O3" t="n">
-        <v>5.324992704696435</v>
+        <v>5.319147187169152</v>
       </c>
       <c r="P3" t="n">
-        <v>314.2836651373983</v>
+        <v>314.2775087803926</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25677,28 +25735,28 @@
         <v>0.0806</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6617829177277348</v>
+        <v>0.6619766013579682</v>
       </c>
       <c r="J4" t="n">
+        <v>428</v>
+      </c>
+      <c r="K4" t="n">
         <v>427</v>
       </c>
-      <c r="K4" t="n">
-        <v>426</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.5570458614405266</v>
+        <v>0.5583800637359007</v>
       </c>
       <c r="M4" t="n">
-        <v>3.391091090037996</v>
+        <v>3.383866365345825</v>
       </c>
       <c r="N4" t="n">
-        <v>19.75322080209523</v>
+        <v>19.7073994521466</v>
       </c>
       <c r="O4" t="n">
-        <v>4.444459562432224</v>
+        <v>4.439301685191783</v>
       </c>
       <c r="P4" t="n">
-        <v>316.8460593413937</v>
+        <v>316.844065366431</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25755,28 +25813,28 @@
         <v>0.09370000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6223140167703687</v>
+        <v>0.6223981403862846</v>
       </c>
       <c r="J5" t="n">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="K5" t="n">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5985587858541732</v>
+        <v>0.5997824574642955</v>
       </c>
       <c r="M5" t="n">
-        <v>2.921231385806809</v>
+        <v>2.914752351512483</v>
       </c>
       <c r="N5" t="n">
-        <v>14.84414684814799</v>
+        <v>14.809547996172</v>
       </c>
       <c r="O5" t="n">
-        <v>3.852810253327821</v>
+        <v>3.848317553967188</v>
       </c>
       <c r="P5" t="n">
-        <v>321.5364806047604</v>
+        <v>321.5356194659204</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -25833,28 +25891,28 @@
         <v>0.09130000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6236488263969284</v>
+        <v>0.6241941899908037</v>
       </c>
       <c r="J6" t="n">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="K6" t="n">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6534863285831425</v>
+        <v>0.6549068728378746</v>
       </c>
       <c r="M6" t="n">
-        <v>2.779357047435647</v>
+        <v>2.775239038716316</v>
       </c>
       <c r="N6" t="n">
-        <v>11.78650419438787</v>
+        <v>11.76248479204181</v>
       </c>
       <c r="O6" t="n">
-        <v>3.433147855014094</v>
+        <v>3.429647910798105</v>
       </c>
       <c r="P6" t="n">
-        <v>326.5720891948583</v>
+        <v>326.5665065321609</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -25911,28 +25969,28 @@
         <v>0.09039999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6512774900526611</v>
+        <v>0.6510715910289965</v>
       </c>
       <c r="J7" t="n">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="K7" t="n">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7503898244228746</v>
+        <v>0.7511636586813828</v>
       </c>
       <c r="M7" t="n">
-        <v>2.324310914285939</v>
+        <v>2.320115669085268</v>
       </c>
       <c r="N7" t="n">
-        <v>8.063589563432808</v>
+        <v>8.045251021266722</v>
       </c>
       <c r="O7" t="n">
-        <v>2.839646027840936</v>
+        <v>2.836415170821564</v>
       </c>
       <c r="P7" t="n">
-        <v>327.7326894507783</v>
+        <v>327.7347971543577</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -25989,28 +26047,28 @@
         <v>0.0853</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6719049899599822</v>
+        <v>0.671791736663197</v>
       </c>
       <c r="J8" t="n">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="K8" t="n">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6874608938528977</v>
+        <v>0.6884227220608793</v>
       </c>
       <c r="M8" t="n">
-        <v>2.763507311788279</v>
+        <v>2.757747231493468</v>
       </c>
       <c r="N8" t="n">
-        <v>11.72986540176596</v>
+        <v>11.70261093802651</v>
       </c>
       <c r="O8" t="n">
-        <v>3.424889107951666</v>
+        <v>3.42090791136308</v>
       </c>
       <c r="P8" t="n">
-        <v>327.9782355942349</v>
+        <v>327.9793949216312</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26067,28 +26125,28 @@
         <v>0.0963</v>
       </c>
       <c r="I9" t="n">
-        <v>0.628125663524311</v>
+        <v>0.628759618534755</v>
       </c>
       <c r="J9" t="n">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="K9" t="n">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6730401154090939</v>
+        <v>0.6744497589037057</v>
       </c>
       <c r="M9" t="n">
-        <v>2.448938385336651</v>
+        <v>2.446508013703944</v>
       </c>
       <c r="N9" t="n">
-        <v>10.95386855789775</v>
+        <v>10.93303076774524</v>
       </c>
       <c r="O9" t="n">
-        <v>3.30966290698883</v>
+        <v>3.306513385387279</v>
       </c>
       <c r="P9" t="n">
-        <v>327.3927006138372</v>
+        <v>327.3862110772629</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26145,28 +26203,28 @@
         <v>0.0804</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6235516212164052</v>
+        <v>0.6240457795285889</v>
       </c>
       <c r="J10" t="n">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="K10" t="n">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6702334925069489</v>
+        <v>0.6715913294043949</v>
       </c>
       <c r="M10" t="n">
-        <v>2.467762208823521</v>
+        <v>2.464100781755415</v>
       </c>
       <c r="N10" t="n">
-        <v>10.93317179496715</v>
+        <v>10.91051634202191</v>
       </c>
       <c r="O10" t="n">
-        <v>3.306534710987797</v>
+        <v>3.303107073956566</v>
       </c>
       <c r="P10" t="n">
-        <v>324.1440475748426</v>
+        <v>324.1389890795432</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -26223,28 +26281,28 @@
         <v>0.08939999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6529700342980782</v>
+        <v>0.6522231274540387</v>
       </c>
       <c r="J11" t="n">
+        <v>428</v>
+      </c>
+      <c r="K11" t="n">
         <v>427</v>
       </c>
-      <c r="K11" t="n">
-        <v>426</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.6489719820139386</v>
+        <v>0.6494403492647578</v>
       </c>
       <c r="M11" t="n">
-        <v>2.640720471027994</v>
+        <v>2.638487571241922</v>
       </c>
       <c r="N11" t="n">
-        <v>13.08101182628665</v>
+        <v>13.05690739967538</v>
       </c>
       <c r="O11" t="n">
-        <v>3.616768146603629</v>
+        <v>3.61343429436255</v>
       </c>
       <c r="P11" t="n">
-        <v>321.421412277554</v>
+        <v>321.4291016911855</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -26301,28 +26359,28 @@
         <v>0.08359999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5997944801947593</v>
+        <v>0.5985914390408889</v>
       </c>
       <c r="J12" t="n">
+        <v>428</v>
+      </c>
+      <c r="K12" t="n">
         <v>427</v>
       </c>
-      <c r="K12" t="n">
-        <v>426</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.5813687924336417</v>
+        <v>0.5812897678577358</v>
       </c>
       <c r="M12" t="n">
-        <v>2.982675846595902</v>
+        <v>2.982328868821011</v>
       </c>
       <c r="N12" t="n">
-        <v>14.69345122309901</v>
+        <v>14.67598209568974</v>
       </c>
       <c r="O12" t="n">
-        <v>3.833203780533851</v>
+        <v>3.830924444006921</v>
       </c>
       <c r="P12" t="n">
-        <v>321.8434044125988</v>
+        <v>321.8557897336352</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -26379,28 +26437,28 @@
         <v>0.1067</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3453851927215664</v>
+        <v>0.3451845360610752</v>
       </c>
       <c r="J13" t="n">
+        <v>428</v>
+      </c>
+      <c r="K13" t="n">
         <v>427</v>
       </c>
-      <c r="K13" t="n">
-        <v>426</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.3234587234712111</v>
+        <v>0.3242580349845369</v>
       </c>
       <c r="M13" t="n">
-        <v>2.923265725466395</v>
+        <v>2.91726073616387</v>
       </c>
       <c r="N13" t="n">
-        <v>14.15213167478006</v>
+        <v>14.11945981731277</v>
       </c>
       <c r="O13" t="n">
-        <v>3.761931907249261</v>
+        <v>3.757586967365196</v>
       </c>
       <c r="P13" t="n">
-        <v>326.052077515373</v>
+        <v>326.0541432777538</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -26438,7 +26496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N428"/>
+  <dimension ref="A1:N429"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57237,6 +57295,78 @@
         </is>
       </c>
     </row>
+    <row r="429">
+      <c r="A429" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:07:59+00:00</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>-42.505438064815905,173.50995347247107</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>-42.506013156137506,173.5094774880287</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>-42.50663870085913,173.50918157196259</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>-42.50726784387048,173.50889851870414</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>-42.50790663203806,173.50864543893059</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>-42.50854319814593,173.5083942071149</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>-42.50918706128172,173.5081806066353</t>
+        </is>
+      </c>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>-42.50983114965252,173.50796984156753</t>
+        </is>
+      </c>
+      <c r="J429" t="inlineStr">
+        <is>
+          <t>-42.51047704426282,173.50776296139674</t>
+        </is>
+      </c>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>-42.51112079526303,173.50754374732907</t>
+        </is>
+      </c>
+      <c r="L429" t="inlineStr">
+        <is>
+          <t>-42.511769217559795,173.50735752192497</t>
+        </is>
+      </c>
+      <c r="M429" t="inlineStr">
+        <is>
+          <t>-42.51242101490537,173.5071967843152</t>
+        </is>
+      </c>
+      <c r="N429" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0396/nzd0396.xlsx
+++ b/data/nzd0396/nzd0396.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N429"/>
+  <dimension ref="A1:N430"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21034,6 +21034,54 @@
       <c r="N429" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:07:30+00:00</t>
+        </is>
+      </c>
+      <c r="B430" t="n">
+        <v>346.9</v>
+      </c>
+      <c r="C430" t="n">
+        <v>332.95</v>
+      </c>
+      <c r="D430" t="n">
+        <v>335.11</v>
+      </c>
+      <c r="E430" t="n">
+        <v>338.43</v>
+      </c>
+      <c r="F430" t="n">
+        <v>344.03</v>
+      </c>
+      <c r="G430" t="n">
+        <v>344.6</v>
+      </c>
+      <c r="H430" t="n">
+        <v>345.6</v>
+      </c>
+      <c r="I430" t="n">
+        <v>345.24</v>
+      </c>
+      <c r="J430" t="n">
+        <v>341.93</v>
+      </c>
+      <c r="K430" t="n">
+        <v>337.25</v>
+      </c>
+      <c r="L430" t="n">
+        <v>335.16</v>
+      </c>
+      <c r="M430" t="n">
+        <v>335.01</v>
+      </c>
+      <c r="N430" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -21048,7 +21096,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B436"/>
+  <dimension ref="A1:B437"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25411,6 +25459,16 @@
       </c>
       <c r="B436" t="n">
         <v>0.17</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B437" t="n">
+        <v>0.53</v>
       </c>
     </row>
   </sheetData>
@@ -25579,28 +25637,28 @@
         <v>0.0562</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7696257866248658</v>
+        <v>0.7706301073145664</v>
       </c>
       <c r="J2" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="K2" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L2" t="n">
-        <v>0.404755429210354</v>
+        <v>0.4064842418387788</v>
       </c>
       <c r="M2" t="n">
-        <v>5.729432781209129</v>
+        <v>5.719437913876791</v>
       </c>
       <c r="N2" t="n">
-        <v>49.9073890712255</v>
+        <v>49.80308470632148</v>
       </c>
       <c r="O2" t="n">
-        <v>7.064516195127979</v>
+        <v>7.0571300615988</v>
       </c>
       <c r="P2" t="n">
-        <v>324.3037425042418</v>
+        <v>324.2934510174417</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25657,28 +25715,28 @@
         <v>0.0827</v>
       </c>
       <c r="I3" t="n">
-        <v>0.638641664100378</v>
+        <v>0.6394453044460247</v>
       </c>
       <c r="J3" t="n">
+        <v>429</v>
+      </c>
+      <c r="K3" t="n">
         <v>428</v>
       </c>
-      <c r="K3" t="n">
-        <v>427</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.4504593341204336</v>
+        <v>0.4522087658853832</v>
       </c>
       <c r="M3" t="n">
-        <v>4.210345901212378</v>
+        <v>4.203705507671137</v>
       </c>
       <c r="N3" t="n">
-        <v>28.29332679876951</v>
+        <v>28.2348413475167</v>
       </c>
       <c r="O3" t="n">
-        <v>5.319147187169152</v>
+        <v>5.313646708948262</v>
       </c>
       <c r="P3" t="n">
-        <v>314.2775087803926</v>
+        <v>314.2692267647462</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25735,28 +25793,28 @@
         <v>0.0806</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6619766013579682</v>
+        <v>0.6623298517165118</v>
       </c>
       <c r="J4" t="n">
+        <v>429</v>
+      </c>
+      <c r="K4" t="n">
         <v>428</v>
       </c>
-      <c r="K4" t="n">
-        <v>427</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.5583800637359007</v>
+        <v>0.5598126535542992</v>
       </c>
       <c r="M4" t="n">
-        <v>3.383866365345825</v>
+        <v>3.377268549018407</v>
       </c>
       <c r="N4" t="n">
-        <v>19.7073994521466</v>
+        <v>19.66282651516869</v>
       </c>
       <c r="O4" t="n">
-        <v>4.439301685191783</v>
+        <v>4.434278578886163</v>
       </c>
       <c r="P4" t="n">
-        <v>316.844065366431</v>
+        <v>316.8404249008765</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25813,28 +25871,28 @@
         <v>0.09370000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6223981403862846</v>
+        <v>0.6226055507911112</v>
       </c>
       <c r="J5" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="K5" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5997824574642955</v>
+        <v>0.6010865736601362</v>
       </c>
       <c r="M5" t="n">
-        <v>2.914752351512483</v>
+        <v>2.908813698260789</v>
       </c>
       <c r="N5" t="n">
-        <v>14.809547996172</v>
+        <v>14.77553997617586</v>
       </c>
       <c r="O5" t="n">
-        <v>3.848317553967188</v>
+        <v>3.84389645752534</v>
       </c>
       <c r="P5" t="n">
-        <v>321.5356194659204</v>
+        <v>321.5334940875773</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -25891,28 +25949,28 @@
         <v>0.09130000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6241941899908037</v>
+        <v>0.6246279965718429</v>
       </c>
       <c r="J6" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="K6" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6549068728378746</v>
+        <v>0.6562621721442025</v>
       </c>
       <c r="M6" t="n">
-        <v>2.775239038716316</v>
+        <v>2.770650970882108</v>
       </c>
       <c r="N6" t="n">
-        <v>11.76248479204181</v>
+        <v>11.73731085557445</v>
       </c>
       <c r="O6" t="n">
-        <v>3.429647910798105</v>
+        <v>3.425975898276934</v>
       </c>
       <c r="P6" t="n">
-        <v>326.5665065321609</v>
+        <v>326.5620612242543</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -25969,28 +26027,28 @@
         <v>0.09039999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6510715910289965</v>
+        <v>0.650929349225464</v>
       </c>
       <c r="J7" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="K7" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7511636586813828</v>
+        <v>0.7519734492292605</v>
       </c>
       <c r="M7" t="n">
-        <v>2.320115669085268</v>
+        <v>2.315560093862118</v>
       </c>
       <c r="N7" t="n">
-        <v>8.045251021266722</v>
+        <v>8.026738829876313</v>
       </c>
       <c r="O7" t="n">
-        <v>2.836415170821564</v>
+        <v>2.833149983653586</v>
       </c>
       <c r="P7" t="n">
-        <v>327.7347971543577</v>
+        <v>327.7362547362421</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26047,28 +26105,28 @@
         <v>0.0853</v>
       </c>
       <c r="I8" t="n">
-        <v>0.671791736663197</v>
+        <v>0.6717413594603043</v>
       </c>
       <c r="J8" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="K8" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6884227220608793</v>
+        <v>0.6894195927498361</v>
       </c>
       <c r="M8" t="n">
-        <v>2.757747231493468</v>
+        <v>2.751627588265892</v>
       </c>
       <c r="N8" t="n">
-        <v>11.70261093802651</v>
+        <v>11.67536239269883</v>
       </c>
       <c r="O8" t="n">
-        <v>3.42090791136308</v>
+        <v>3.416922942165777</v>
       </c>
       <c r="P8" t="n">
-        <v>327.9793949216312</v>
+        <v>327.979911147498</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26125,28 +26183,28 @@
         <v>0.0963</v>
       </c>
       <c r="I9" t="n">
-        <v>0.628759618534755</v>
+        <v>0.6293127665012457</v>
       </c>
       <c r="J9" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="K9" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6744497589037057</v>
+        <v>0.675815813297753</v>
       </c>
       <c r="M9" t="n">
-        <v>2.446508013703944</v>
+        <v>2.443664023252844</v>
       </c>
       <c r="N9" t="n">
-        <v>10.93303076774524</v>
+        <v>10.91119505831738</v>
       </c>
       <c r="O9" t="n">
-        <v>3.306513385387279</v>
+        <v>3.303209811428481</v>
       </c>
       <c r="P9" t="n">
-        <v>327.3862110772629</v>
+        <v>327.3805428529059</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26203,28 +26261,28 @@
         <v>0.0804</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6240457795285889</v>
+        <v>0.6246275466552591</v>
       </c>
       <c r="J10" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="K10" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6715913294043949</v>
+        <v>0.6729786710026726</v>
       </c>
       <c r="M10" t="n">
-        <v>2.464100781755415</v>
+        <v>2.460822557211137</v>
       </c>
       <c r="N10" t="n">
-        <v>10.91051634202191</v>
+        <v>10.88912049321155</v>
       </c>
       <c r="O10" t="n">
-        <v>3.303107073956566</v>
+        <v>3.299866738704997</v>
       </c>
       <c r="P10" t="n">
-        <v>324.1389890795432</v>
+        <v>324.1330275885909</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -26281,28 +26339,28 @@
         <v>0.08939999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6522231274540387</v>
+        <v>0.6516049133121968</v>
       </c>
       <c r="J11" t="n">
+        <v>429</v>
+      </c>
+      <c r="K11" t="n">
         <v>428</v>
       </c>
-      <c r="K11" t="n">
-        <v>427</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.6494403492647578</v>
+        <v>0.6500267583459238</v>
       </c>
       <c r="M11" t="n">
-        <v>2.638487571241922</v>
+        <v>2.63557969351221</v>
       </c>
       <c r="N11" t="n">
-        <v>13.05690739967538</v>
+        <v>13.03091017703943</v>
       </c>
       <c r="O11" t="n">
-        <v>3.61343429436255</v>
+        <v>3.609835200814496</v>
       </c>
       <c r="P11" t="n">
-        <v>321.4291016911855</v>
+        <v>321.4354727740004</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -26359,28 +26417,28 @@
         <v>0.08359999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5985914390408889</v>
+        <v>0.5974844639374192</v>
       </c>
       <c r="J12" t="n">
+        <v>429</v>
+      </c>
+      <c r="K12" t="n">
         <v>428</v>
       </c>
-      <c r="K12" t="n">
-        <v>427</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.5812897678577358</v>
+        <v>0.5813215084504635</v>
       </c>
       <c r="M12" t="n">
-        <v>2.982328868821011</v>
+        <v>2.981443251739883</v>
       </c>
       <c r="N12" t="n">
-        <v>14.67598209568974</v>
+        <v>14.65615124294202</v>
       </c>
       <c r="O12" t="n">
-        <v>3.830924444006921</v>
+        <v>3.828335309627674</v>
       </c>
       <c r="P12" t="n">
-        <v>321.8557897336352</v>
+        <v>321.8671978033978</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -26437,28 +26495,28 @@
         <v>0.1067</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3451845360610752</v>
+        <v>0.3451145272170468</v>
       </c>
       <c r="J13" t="n">
+        <v>429</v>
+      </c>
+      <c r="K13" t="n">
         <v>428</v>
       </c>
-      <c r="K13" t="n">
-        <v>427</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.3242580349845369</v>
+        <v>0.3252250087671467</v>
       </c>
       <c r="M13" t="n">
-        <v>2.91726073616387</v>
+        <v>2.91073674196231</v>
       </c>
       <c r="N13" t="n">
-        <v>14.11945981731277</v>
+        <v>14.0865282565368</v>
       </c>
       <c r="O13" t="n">
-        <v>3.757586967365196</v>
+        <v>3.753202400156005</v>
       </c>
       <c r="P13" t="n">
-        <v>326.0541432777538</v>
+        <v>326.0548647626131</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -26496,7 +26554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N429"/>
+  <dimension ref="A1:N430"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57367,6 +57425,78 @@
         </is>
       </c>
     </row>
+    <row r="430">
+      <c r="A430" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:07:30+00:00</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>-42.50544096734058,173.50996383036824</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>-42.50601475094949,173.50948317922393</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>-42.50663991292316,173.5091858973106</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>-42.50726876887162,173.50890181965826</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>-42.507906005895684,173.50864289839083</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>-42.50854357548883,173.50839608664648</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>-42.509187404162724,173.50818249820958</t>
+        </is>
+      </c>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t>-42.50983087522064,173.50796805382538</t>
+        </is>
+      </c>
+      <c r="J430" t="inlineStr">
+        <is>
+          <t>-42.51047741019214,173.50776571697548</t>
+        </is>
+      </c>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>-42.511121256305344,173.50754722187423</t>
+        </is>
+      </c>
+      <c r="L430" t="inlineStr">
+        <is>
+          <t>-42.5117695307532,173.50735991933445</t>
+        </is>
+      </c>
+      <c r="M430" t="inlineStr">
+        <is>
+          <t>-42.51242147790526,173.50720038207538</t>
+        </is>
+      </c>
+      <c r="N430" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0396/nzd0396.xlsx
+++ b/data/nzd0396/nzd0396.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N430"/>
+  <dimension ref="A1:N431"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21082,6 +21082,54 @@
       <c r="N430" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:07:22+00:00</t>
+        </is>
+      </c>
+      <c r="B431" t="n">
+        <v>347.42</v>
+      </c>
+      <c r="C431" t="n">
+        <v>333.64</v>
+      </c>
+      <c r="D431" t="n">
+        <v>335.09</v>
+      </c>
+      <c r="E431" t="n">
+        <v>337.1</v>
+      </c>
+      <c r="F431" t="n">
+        <v>341.93</v>
+      </c>
+      <c r="G431" t="n">
+        <v>342.2</v>
+      </c>
+      <c r="H431" t="n">
+        <v>343.84</v>
+      </c>
+      <c r="I431" t="n">
+        <v>343.29</v>
+      </c>
+      <c r="J431" t="n">
+        <v>339.81</v>
+      </c>
+      <c r="K431" t="n">
+        <v>335.07</v>
+      </c>
+      <c r="L431" t="n">
+        <v>334.06</v>
+      </c>
+      <c r="M431" t="n">
+        <v>334.15</v>
+      </c>
+      <c r="N431" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -21096,7 +21144,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B437"/>
+  <dimension ref="A1:B438"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25469,6 +25517,16 @@
       </c>
       <c r="B437" t="n">
         <v>0.53</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B438" t="n">
+        <v>-0.35</v>
       </c>
     </row>
   </sheetData>
@@ -25637,28 +25695,28 @@
         <v>0.0562</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7706301073145664</v>
+        <v>0.771805288999483</v>
       </c>
       <c r="J2" t="n">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="K2" t="n">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4064842418387788</v>
+        <v>0.4083328392365302</v>
       </c>
       <c r="M2" t="n">
-        <v>5.719437913876791</v>
+        <v>5.709964977341838</v>
       </c>
       <c r="N2" t="n">
-        <v>49.80308470632148</v>
+        <v>49.70334541045729</v>
       </c>
       <c r="O2" t="n">
-        <v>7.0571300615988</v>
+        <v>7.050059957933499</v>
       </c>
       <c r="P2" t="n">
-        <v>324.2934510174417</v>
+        <v>324.2812977608046</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25715,28 +25773,28 @@
         <v>0.0827</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6394453044460247</v>
+        <v>0.6405076081912345</v>
       </c>
       <c r="J3" t="n">
+        <v>430</v>
+      </c>
+      <c r="K3" t="n">
         <v>429</v>
       </c>
-      <c r="K3" t="n">
-        <v>428</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.4522087658853832</v>
+        <v>0.4541435499698534</v>
       </c>
       <c r="M3" t="n">
-        <v>4.203705507671137</v>
+        <v>4.198031093247659</v>
       </c>
       <c r="N3" t="n">
-        <v>28.2348413475167</v>
+        <v>28.18202540533684</v>
       </c>
       <c r="O3" t="n">
-        <v>5.313646708948262</v>
+        <v>5.308674543173357</v>
       </c>
       <c r="P3" t="n">
-        <v>314.2692267647462</v>
+        <v>314.2581788841278</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25793,28 +25851,28 @@
         <v>0.0806</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6623298517165118</v>
+        <v>0.6626139116535781</v>
       </c>
       <c r="J4" t="n">
+        <v>430</v>
+      </c>
+      <c r="K4" t="n">
         <v>429</v>
       </c>
-      <c r="K4" t="n">
-        <v>428</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.5598126535542992</v>
+        <v>0.5612313983820044</v>
       </c>
       <c r="M4" t="n">
-        <v>3.377268549018407</v>
+        <v>3.370426450876223</v>
       </c>
       <c r="N4" t="n">
-        <v>19.66282651516869</v>
+        <v>19.61792192307949</v>
       </c>
       <c r="O4" t="n">
-        <v>4.434278578886163</v>
+        <v>4.42921233664401</v>
       </c>
       <c r="P4" t="n">
-        <v>316.8404249008765</v>
+        <v>316.8374706984769</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25871,28 +25929,28 @@
         <v>0.09370000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6226055507911112</v>
+        <v>0.6221643734321342</v>
       </c>
       <c r="J5" t="n">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="K5" t="n">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6010865736601362</v>
+        <v>0.6018923358069255</v>
       </c>
       <c r="M5" t="n">
-        <v>2.908813698260789</v>
+        <v>2.904860325860308</v>
       </c>
       <c r="N5" t="n">
-        <v>14.77553997617586</v>
+        <v>14.74344473538886</v>
       </c>
       <c r="O5" t="n">
-        <v>3.84389645752534</v>
+        <v>3.83971935633177</v>
       </c>
       <c r="P5" t="n">
-        <v>321.5334940875773</v>
+        <v>321.5380565664987</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -25949,28 +26007,28 @@
         <v>0.09130000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6246279965718429</v>
+        <v>0.6240744572741596</v>
       </c>
       <c r="J6" t="n">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="K6" t="n">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6562621721442025</v>
+        <v>0.6569059600389147</v>
       </c>
       <c r="M6" t="n">
-        <v>2.770650970882108</v>
+        <v>2.767603045072411</v>
       </c>
       <c r="N6" t="n">
-        <v>11.73731085557445</v>
+        <v>11.71358276365538</v>
       </c>
       <c r="O6" t="n">
-        <v>3.425975898276934</v>
+        <v>3.422511178017594</v>
       </c>
       <c r="P6" t="n">
-        <v>326.5620612242543</v>
+        <v>326.5677857051833</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26027,28 +26085,28 @@
         <v>0.09039999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.650929349225464</v>
+        <v>0.6496608045534611</v>
       </c>
       <c r="J7" t="n">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="K7" t="n">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7519734492292605</v>
+        <v>0.7517298459626564</v>
       </c>
       <c r="M7" t="n">
-        <v>2.315560093862118</v>
+        <v>2.317644852055014</v>
       </c>
       <c r="N7" t="n">
-        <v>8.026738829876313</v>
+        <v>8.026810589574753</v>
       </c>
       <c r="O7" t="n">
-        <v>2.833149983653586</v>
+        <v>2.833162647921004</v>
       </c>
       <c r="P7" t="n">
-        <v>327.7362547362421</v>
+        <v>327.7493735153656</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26105,28 +26163,28 @@
         <v>0.0853</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6717413594603043</v>
+        <v>0.670850137506616</v>
       </c>
       <c r="J8" t="n">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="K8" t="n">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6894195927498361</v>
+        <v>0.6897372662505191</v>
       </c>
       <c r="M8" t="n">
-        <v>2.751627588265892</v>
+        <v>2.75059547520352</v>
       </c>
       <c r="N8" t="n">
-        <v>11.67536239269883</v>
+        <v>11.6574594392573</v>
       </c>
       <c r="O8" t="n">
-        <v>3.416922942165777</v>
+        <v>3.414302189211919</v>
       </c>
       <c r="P8" t="n">
-        <v>327.979911147498</v>
+        <v>327.9891278067285</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26183,28 +26241,28 @@
         <v>0.0963</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6293127665012457</v>
+        <v>0.6289473576162442</v>
       </c>
       <c r="J9" t="n">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="K9" t="n">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="L9" t="n">
-        <v>0.675815813297753</v>
+        <v>0.6766102764665864</v>
       </c>
       <c r="M9" t="n">
-        <v>2.443664023252844</v>
+        <v>2.439923632201162</v>
       </c>
       <c r="N9" t="n">
-        <v>10.91119505831738</v>
+        <v>10.88737501884339</v>
       </c>
       <c r="O9" t="n">
-        <v>3.303209811428481</v>
+        <v>3.299602251612063</v>
       </c>
       <c r="P9" t="n">
-        <v>327.3805428529059</v>
+        <v>327.3843217647234</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26261,28 +26319,28 @@
         <v>0.0804</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6246275466552591</v>
+        <v>0.6242106274938124</v>
       </c>
       <c r="J10" t="n">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="K10" t="n">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6729786710026726</v>
+        <v>0.6737289821603558</v>
       </c>
       <c r="M10" t="n">
-        <v>2.460822557211137</v>
+        <v>2.457698969666129</v>
       </c>
       <c r="N10" t="n">
-        <v>10.88912049321155</v>
+        <v>10.86582104422955</v>
       </c>
       <c r="O10" t="n">
-        <v>3.299866738704997</v>
+        <v>3.296334486096571</v>
       </c>
       <c r="P10" t="n">
-        <v>324.1330275885909</v>
+        <v>324.1373391989836</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -26339,28 +26397,28 @@
         <v>0.08939999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6516049133121968</v>
+        <v>0.6499498063422531</v>
       </c>
       <c r="J11" t="n">
+        <v>430</v>
+      </c>
+      <c r="K11" t="n">
         <v>429</v>
       </c>
-      <c r="K11" t="n">
-        <v>428</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.6500267583459238</v>
+        <v>0.6494437614433277</v>
       </c>
       <c r="M11" t="n">
-        <v>2.63557969351221</v>
+        <v>2.637988836357743</v>
       </c>
       <c r="N11" t="n">
-        <v>13.03091017703943</v>
+        <v>13.03209114646306</v>
       </c>
       <c r="O11" t="n">
-        <v>3.609835200814496</v>
+        <v>3.609998773748138</v>
       </c>
       <c r="P11" t="n">
-        <v>321.4354727740004</v>
+        <v>321.4526857644443</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -26417,28 +26475,28 @@
         <v>0.08359999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5974844639374192</v>
+        <v>0.5958266698821685</v>
       </c>
       <c r="J12" t="n">
+        <v>430</v>
+      </c>
+      <c r="K12" t="n">
         <v>429</v>
       </c>
-      <c r="K12" t="n">
-        <v>428</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.5813215084504635</v>
+        <v>0.58064703400595</v>
       </c>
       <c r="M12" t="n">
-        <v>2.981443251739883</v>
+        <v>2.983457208824851</v>
       </c>
       <c r="N12" t="n">
-        <v>14.65615124294202</v>
+        <v>14.65364631805656</v>
       </c>
       <c r="O12" t="n">
-        <v>3.828335309627674</v>
+        <v>3.828008139758399</v>
       </c>
       <c r="P12" t="n">
-        <v>321.8671978033978</v>
+        <v>321.8844387393306</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -26495,28 +26553,28 @@
         <v>0.1067</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3451145272170468</v>
+        <v>0.3446288166577544</v>
       </c>
       <c r="J13" t="n">
+        <v>430</v>
+      </c>
+      <c r="K13" t="n">
         <v>429</v>
       </c>
-      <c r="K13" t="n">
-        <v>428</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.3252250087671467</v>
+        <v>0.3256506862790591</v>
       </c>
       <c r="M13" t="n">
-        <v>2.91073674196231</v>
+        <v>2.905950473881675</v>
       </c>
       <c r="N13" t="n">
-        <v>14.0865282565368</v>
+        <v>14.05641012681226</v>
       </c>
       <c r="O13" t="n">
-        <v>3.753202400156005</v>
+        <v>3.749187928980389</v>
       </c>
       <c r="P13" t="n">
-        <v>326.0548647626131</v>
+        <v>326.0599161166145</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -26554,7 +26612,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N430"/>
+  <dimension ref="A1:N431"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57497,6 +57555,78 @@
         </is>
       </c>
     </row>
+    <row r="431">
+      <c r="A431" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:07:22+00:00</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>-42.50544262592569,173.509969749167</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>-42.506016951789555,173.50949103307386</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>-42.50663984913033,173.50918566966072</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>-42.507264526624205,173.50888668080054</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>-42.50790002907918,173.50861864778682</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>-42.50853791534223,173.5083678936749</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>-42.50918363246989,173.50816169089364</t>
+        </is>
+      </c>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>-42.50982730760386,173.5079448131787</t>
+        </is>
+      </c>
+      <c r="J431" t="inlineStr">
+        <is>
+          <t>-42.5104740372759,173.50774031772912</t>
+        </is>
+      </c>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>-42.511117790536396,173.50752110288056</t>
+        </is>
+      </c>
+      <c r="L431" t="inlineStr">
+        <is>
+          <t>-42.51176780818877,173.50734673358258</t>
+        </is>
+      </c>
+      <c r="M431" t="inlineStr">
+        <is>
+          <t>-42.512420150638604,173.50719006849627</t>
+        </is>
+      </c>
+      <c r="N431" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0396/nzd0396.xlsx
+++ b/data/nzd0396/nzd0396.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N431"/>
+  <dimension ref="A1:N433"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21128,6 +21128,102 @@
         <v>334.15</v>
       </c>
       <c r="N431" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:07:20+00:00</t>
+        </is>
+      </c>
+      <c r="B432" t="n">
+        <v>347.34</v>
+      </c>
+      <c r="C432" t="n">
+        <v>333.21</v>
+      </c>
+      <c r="D432" t="n">
+        <v>335.11</v>
+      </c>
+      <c r="E432" t="n">
+        <v>337.23</v>
+      </c>
+      <c r="F432" t="n">
+        <v>341.04</v>
+      </c>
+      <c r="G432" t="n">
+        <v>341.74</v>
+      </c>
+      <c r="H432" t="n">
+        <v>343.38</v>
+      </c>
+      <c r="I432" t="n">
+        <v>342.15</v>
+      </c>
+      <c r="J432" t="n">
+        <v>337.98</v>
+      </c>
+      <c r="K432" t="n">
+        <v>334.78</v>
+      </c>
+      <c r="L432" t="n">
+        <v>333.29</v>
+      </c>
+      <c r="M432" t="n">
+        <v>333.14</v>
+      </c>
+      <c r="N432" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:07:33+00:00</t>
+        </is>
+      </c>
+      <c r="B433" t="n">
+        <v>345.91</v>
+      </c>
+      <c r="C433" t="n">
+        <v>332.37</v>
+      </c>
+      <c r="D433" t="n">
+        <v>335.09</v>
+      </c>
+      <c r="E433" t="n">
+        <v>336.74</v>
+      </c>
+      <c r="F433" t="n">
+        <v>339.2</v>
+      </c>
+      <c r="G433" t="n">
+        <v>340.44</v>
+      </c>
+      <c r="H433" t="n">
+        <v>341.47</v>
+      </c>
+      <c r="I433" t="n">
+        <v>339.73</v>
+      </c>
+      <c r="J433" t="n">
+        <v>335.99</v>
+      </c>
+      <c r="K433" t="n">
+        <v>333.57</v>
+      </c>
+      <c r="L433" t="n">
+        <v>332.18</v>
+      </c>
+      <c r="M433" t="n">
+        <v>332.08</v>
+      </c>
+      <c r="N433" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -21144,7 +21240,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B438"/>
+  <dimension ref="A1:B440"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25527,6 +25623,26 @@
       </c>
       <c r="B438" t="n">
         <v>-0.35</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B439" t="n">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B440" t="n">
+        <v>0.32</v>
       </c>
     </row>
   </sheetData>
@@ -25695,28 +25811,28 @@
         <v>0.0562</v>
       </c>
       <c r="I2" t="n">
-        <v>0.771805288999483</v>
+        <v>0.7733707784292478</v>
       </c>
       <c r="J2" t="n">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="K2" t="n">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4083328392365302</v>
+        <v>0.4116113625507309</v>
       </c>
       <c r="M2" t="n">
-        <v>5.709964977341838</v>
+        <v>5.68859428229457</v>
       </c>
       <c r="N2" t="n">
-        <v>49.70334541045729</v>
+        <v>49.49009334537409</v>
       </c>
       <c r="O2" t="n">
-        <v>7.050059957933499</v>
+        <v>7.034919569218549</v>
       </c>
       <c r="P2" t="n">
-        <v>324.2812977608046</v>
+        <v>324.2650663937976</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25773,28 +25889,28 @@
         <v>0.0827</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6405076081912345</v>
+        <v>0.6418006901043561</v>
       </c>
       <c r="J3" t="n">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="K3" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4541435499698534</v>
+        <v>0.4574999061445103</v>
       </c>
       <c r="M3" t="n">
-        <v>4.198031093247659</v>
+        <v>4.183515089369123</v>
       </c>
       <c r="N3" t="n">
-        <v>28.18202540533684</v>
+        <v>28.06181077424585</v>
       </c>
       <c r="O3" t="n">
-        <v>5.308674543173357</v>
+        <v>5.297339971556088</v>
       </c>
       <c r="P3" t="n">
-        <v>314.2581788841278</v>
+        <v>314.2446949500537</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25851,28 +25967,28 @@
         <v>0.0806</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6626139116535781</v>
+        <v>0.6631477545895361</v>
       </c>
       <c r="J4" t="n">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="K4" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5612313983820044</v>
+        <v>0.5640366509319727</v>
       </c>
       <c r="M4" t="n">
-        <v>3.370426450876223</v>
+        <v>3.356699474814173</v>
       </c>
       <c r="N4" t="n">
-        <v>19.61792192307949</v>
+        <v>19.52854045753188</v>
       </c>
       <c r="O4" t="n">
-        <v>4.42921233664401</v>
+        <v>4.419110822046883</v>
       </c>
       <c r="P4" t="n">
-        <v>316.8374706984769</v>
+        <v>316.8319024898054</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -25929,28 +26045,28 @@
         <v>0.09370000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6221643734321342</v>
+        <v>0.6211594221311781</v>
       </c>
       <c r="J5" t="n">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="K5" t="n">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6018923358069255</v>
+        <v>0.6033736117699604</v>
       </c>
       <c r="M5" t="n">
-        <v>2.904860325860308</v>
+        <v>2.897782477114975</v>
       </c>
       <c r="N5" t="n">
-        <v>14.74344473538886</v>
+        <v>14.68139356341929</v>
       </c>
       <c r="O5" t="n">
-        <v>3.83971935633177</v>
+        <v>3.831630666363772</v>
       </c>
       <c r="P5" t="n">
-        <v>321.5380565664987</v>
+        <v>321.5484828014742</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26007,28 +26123,28 @@
         <v>0.09130000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6240744572741596</v>
+        <v>0.6213517146785096</v>
       </c>
       <c r="J6" t="n">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="K6" t="n">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6569059600389147</v>
+        <v>0.6562390052379581</v>
       </c>
       <c r="M6" t="n">
-        <v>2.767603045072411</v>
+        <v>2.771317980057909</v>
       </c>
       <c r="N6" t="n">
-        <v>11.71358276365538</v>
+        <v>11.70672437445505</v>
       </c>
       <c r="O6" t="n">
-        <v>3.422511178017594</v>
+        <v>3.421509078528807</v>
       </c>
       <c r="P6" t="n">
-        <v>326.5677857051833</v>
+        <v>326.5960360355617</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26085,28 +26201,28 @@
         <v>0.09039999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6496608045534611</v>
+        <v>0.6461493102311788</v>
       </c>
       <c r="J7" t="n">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="K7" t="n">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7517298459626564</v>
+        <v>0.7498137975303564</v>
       </c>
       <c r="M7" t="n">
-        <v>2.317644852055014</v>
+        <v>2.327385536142221</v>
       </c>
       <c r="N7" t="n">
-        <v>8.026810589574753</v>
+        <v>8.063833115957566</v>
       </c>
       <c r="O7" t="n">
-        <v>2.833162647921004</v>
+        <v>2.839688911827767</v>
       </c>
       <c r="P7" t="n">
-        <v>327.7493735153656</v>
+        <v>327.7858027619547</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26163,28 +26279,28 @@
         <v>0.0853</v>
       </c>
       <c r="I8" t="n">
-        <v>0.670850137506616</v>
+        <v>0.6678065891667814</v>
       </c>
       <c r="J8" t="n">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="K8" t="n">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6897372662505191</v>
+        <v>0.6888199295643842</v>
       </c>
       <c r="M8" t="n">
-        <v>2.75059547520352</v>
+        <v>2.756006118214771</v>
       </c>
       <c r="N8" t="n">
-        <v>11.6574594392573</v>
+        <v>11.66200717619743</v>
       </c>
       <c r="O8" t="n">
-        <v>3.414302189211919</v>
+        <v>3.414968107639869</v>
       </c>
       <c r="P8" t="n">
-        <v>327.9891278067285</v>
+        <v>328.0207060491059</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26241,28 +26357,28 @@
         <v>0.0963</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6289473576162442</v>
+        <v>0.6261108799931567</v>
       </c>
       <c r="J9" t="n">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="K9" t="n">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6766102764665864</v>
+        <v>0.675698216859383</v>
       </c>
       <c r="M9" t="n">
-        <v>2.439923632201162</v>
+        <v>2.443615353652288</v>
       </c>
       <c r="N9" t="n">
-        <v>10.88737501884339</v>
+        <v>10.89092829956636</v>
       </c>
       <c r="O9" t="n">
-        <v>3.299602251612063</v>
+        <v>3.300140648452178</v>
       </c>
       <c r="P9" t="n">
-        <v>327.3843217647234</v>
+        <v>327.4137544871806</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26319,28 +26435,28 @@
         <v>0.0804</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6242106274938124</v>
+        <v>0.6208650215504217</v>
       </c>
       <c r="J10" t="n">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="K10" t="n">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6737289821603558</v>
+        <v>0.672106370783276</v>
       </c>
       <c r="M10" t="n">
-        <v>2.457698969666129</v>
+        <v>2.466968303245317</v>
       </c>
       <c r="N10" t="n">
-        <v>10.86582104422955</v>
+        <v>10.88567055810736</v>
       </c>
       <c r="O10" t="n">
-        <v>3.296334486096571</v>
+        <v>3.299343958745035</v>
       </c>
       <c r="P10" t="n">
-        <v>324.1373391989836</v>
+        <v>324.1720508968023</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -26397,28 +26513,28 @@
         <v>0.08939999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6499498063422531</v>
+        <v>0.6458623250651183</v>
       </c>
       <c r="J11" t="n">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="K11" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6494437614433277</v>
+        <v>0.6470939535479698</v>
       </c>
       <c r="M11" t="n">
-        <v>2.637988836357743</v>
+        <v>2.646823467479838</v>
       </c>
       <c r="N11" t="n">
-        <v>13.03209114646306</v>
+        <v>13.0700781647256</v>
       </c>
       <c r="O11" t="n">
-        <v>3.609998773748138</v>
+        <v>3.615256306920106</v>
       </c>
       <c r="P11" t="n">
-        <v>321.4526857644443</v>
+        <v>321.4953273375843</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -26475,28 +26591,28 @@
         <v>0.08359999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5958266698821685</v>
+        <v>0.591353191061851</v>
       </c>
       <c r="J12" t="n">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="K12" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="L12" t="n">
-        <v>0.58064703400595</v>
+        <v>0.5774270959410448</v>
       </c>
       <c r="M12" t="n">
-        <v>2.983457208824851</v>
+        <v>2.994091395740163</v>
       </c>
       <c r="N12" t="n">
-        <v>14.65364631805656</v>
+        <v>14.70296420684254</v>
       </c>
       <c r="O12" t="n">
-        <v>3.828008139758399</v>
+        <v>3.834444445658659</v>
       </c>
       <c r="P12" t="n">
-        <v>321.8844387393306</v>
+        <v>321.9311061259671</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -26553,28 +26669,28 @@
         <v>0.1067</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3446288166577544</v>
+        <v>0.3422838228858139</v>
       </c>
       <c r="J13" t="n">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="K13" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="L13" t="n">
-        <v>0.3256506862790591</v>
+        <v>0.324301967240881</v>
       </c>
       <c r="M13" t="n">
-        <v>2.905950473881675</v>
+        <v>2.902235731126567</v>
       </c>
       <c r="N13" t="n">
-        <v>14.05641012681226</v>
+        <v>14.0243371262102</v>
       </c>
       <c r="O13" t="n">
-        <v>3.749187928980389</v>
+        <v>3.744908159916635</v>
       </c>
       <c r="P13" t="n">
-        <v>326.0599161166145</v>
+        <v>326.0843813331236</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -26612,7 +26728,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N431"/>
+  <dimension ref="A1:N433"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57627,6 +57743,150 @@
         </is>
       </c>
     </row>
+    <row r="432">
+      <c r="A432" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:07:20+00:00</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>-42.50544237075878,173.50996883858258</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>-42.50601558025161,173.5094861386456</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>-42.50663991292316,173.5091858973106</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>-42.50726494128006,173.50888816053845</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>-42.50789749604588,173.50860837015128</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>-42.50853683048,173.50836249002253</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>-42.509182646685915,173.5081562526183</t>
+        </is>
+      </c>
+      <c r="I432" t="inlineStr">
+        <is>
+          <t>-42.50982522191799,173.5079312263403</t>
+        </is>
+      </c>
+      <c r="J432" t="inlineStr">
+        <is>
+          <t>-42.51047112574459,173.5077183929101</t>
+        </is>
+      </c>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>-42.51111732949329,173.50751762833573</t>
+        </is>
+      </c>
+      <c r="L432" t="inlineStr">
+        <is>
+          <t>-42.511766602392775,173.5073375035567</t>
+        </is>
+      </c>
+      <c r="M432" t="inlineStr">
+        <is>
+          <t>-42.512418591870755,173.50717795603762</t>
+        </is>
+      </c>
+      <c r="N432" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:07:33+00:00</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>-42.505437809648846,173.50995256188673</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>-42.50601290096756,173.50947657743748</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>-42.50663984913033,173.50918566966072</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>-42.50726337834638,173.50888258306497</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>-42.50789225921004,173.50858712200846</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>-42.508533764563616,173.5083472188322</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>-42.5091785535366,173.50813367195508</t>
+        </is>
+      </c>
+      <c r="I433" t="inlineStr">
+        <is>
+          <t>-42.509820794404064,173.50790238410738</t>
+        </is>
+      </c>
+      <c r="J433" t="inlineStr">
+        <is>
+          <t>-42.510467959648395,173.5076945511693</t>
+        </is>
+      </c>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>-42.51111540582952,173.50750313109754</t>
+        </is>
+      </c>
+      <c r="L433" t="inlineStr">
+        <is>
+          <t>-42.511764864166054,173.50732419793556</t>
+        </is>
+      </c>
+      <c r="M433" t="inlineStr">
+        <is>
+          <t>-42.512416955934825,173.50716524395295</t>
+        </is>
+      </c>
+      <c r="N433" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0396/nzd0396.xlsx
+++ b/data/nzd0396/nzd0396.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N433"/>
+  <dimension ref="A1:N436"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21224,6 +21224,150 @@
         <v>332.08</v>
       </c>
       <c r="N433" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-07 22:07:26+00:00</t>
+        </is>
+      </c>
+      <c r="B434" t="n">
+        <v>346.56</v>
+      </c>
+      <c r="C434" t="n">
+        <v>332.02</v>
+      </c>
+      <c r="D434" t="n">
+        <v>335.24</v>
+      </c>
+      <c r="E434" t="n">
+        <v>336.63</v>
+      </c>
+      <c r="F434" t="n">
+        <v>338.88</v>
+      </c>
+      <c r="G434" t="n">
+        <v>343.08</v>
+      </c>
+      <c r="H434" t="n">
+        <v>341.01</v>
+      </c>
+      <c r="I434" t="n">
+        <v>339.4</v>
+      </c>
+      <c r="J434" t="n">
+        <v>335.65</v>
+      </c>
+      <c r="K434" t="n">
+        <v>332.16</v>
+      </c>
+      <c r="L434" t="n">
+        <v>329.98</v>
+      </c>
+      <c r="M434" t="n">
+        <v>331.43</v>
+      </c>
+      <c r="N434" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:06:47+00:00</t>
+        </is>
+      </c>
+      <c r="B435" t="n">
+        <v>344.17</v>
+      </c>
+      <c r="C435" t="n">
+        <v>330.8</v>
+      </c>
+      <c r="D435" t="n">
+        <v>334.37</v>
+      </c>
+      <c r="E435" t="n">
+        <v>335.7</v>
+      </c>
+      <c r="F435" t="n">
+        <v>338.75</v>
+      </c>
+      <c r="G435" t="n">
+        <v>343.07</v>
+      </c>
+      <c r="H435" t="n">
+        <v>340.66</v>
+      </c>
+      <c r="I435" t="n">
+        <v>338.78</v>
+      </c>
+      <c r="J435" t="n">
+        <v>335.64</v>
+      </c>
+      <c r="K435" t="n">
+        <v>332.09</v>
+      </c>
+      <c r="L435" t="n">
+        <v>329.19</v>
+      </c>
+      <c r="M435" t="n">
+        <v>330.61</v>
+      </c>
+      <c r="N435" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:58+00:00</t>
+        </is>
+      </c>
+      <c r="B436" t="n">
+        <v>344.21</v>
+      </c>
+      <c r="C436" t="n">
+        <v>330.18</v>
+      </c>
+      <c r="D436" t="n">
+        <v>333.88</v>
+      </c>
+      <c r="E436" t="n">
+        <v>335.83</v>
+      </c>
+      <c r="F436" t="n">
+        <v>338.87</v>
+      </c>
+      <c r="G436" t="n">
+        <v>342.96</v>
+      </c>
+      <c r="H436" t="n">
+        <v>340.68</v>
+      </c>
+      <c r="I436" t="n">
+        <v>338.44</v>
+      </c>
+      <c r="J436" t="n">
+        <v>336.23</v>
+      </c>
+      <c r="K436" t="n">
+        <v>332.36</v>
+      </c>
+      <c r="L436" t="n">
+        <v>329.28</v>
+      </c>
+      <c r="M436" t="n">
+        <v>330.94</v>
+      </c>
+      <c r="N436" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -21240,7 +21384,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B440"/>
+  <dimension ref="A1:B443"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25643,6 +25787,36 @@
       </c>
       <c r="B440" t="n">
         <v>0.32</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>2026-04-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B441" t="n">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B442" t="n">
+        <v>-0.68</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B443" t="n">
+        <v>0.6</v>
       </c>
     </row>
   </sheetData>
@@ -25811,28 +25985,28 @@
         <v>0.0562</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7733707784292478</v>
+        <v>0.7734120976944007</v>
       </c>
       <c r="J2" t="n">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="K2" t="n">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4116113625507309</v>
+        <v>0.415145265059165</v>
       </c>
       <c r="M2" t="n">
-        <v>5.68859428229457</v>
+        <v>5.656537457741214</v>
       </c>
       <c r="N2" t="n">
-        <v>49.49009334537409</v>
+        <v>49.15755983809073</v>
       </c>
       <c r="O2" t="n">
-        <v>7.034919569218549</v>
+        <v>7.01124524161655</v>
       </c>
       <c r="P2" t="n">
-        <v>324.2650663937976</v>
+        <v>324.2646469576103</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -25889,28 +26063,28 @@
         <v>0.0827</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6418006901043561</v>
+        <v>0.6412625554209999</v>
       </c>
       <c r="J3" t="n">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="K3" t="n">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4574999061445103</v>
+        <v>0.460684561924208</v>
       </c>
       <c r="M3" t="n">
-        <v>4.183515089369123</v>
+        <v>4.161036147352966</v>
       </c>
       <c r="N3" t="n">
-        <v>28.06181077424585</v>
+        <v>27.873142588289</v>
       </c>
       <c r="O3" t="n">
-        <v>5.297339971556088</v>
+        <v>5.27950211556819</v>
       </c>
       <c r="P3" t="n">
-        <v>314.2446949500537</v>
+        <v>314.2503389187501</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -25967,28 +26141,28 @@
         <v>0.0806</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6631477545895361</v>
+        <v>0.6630531497936767</v>
       </c>
       <c r="J4" t="n">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="K4" t="n">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5640366509319727</v>
+        <v>0.5675469943993632</v>
       </c>
       <c r="M4" t="n">
-        <v>3.356699474814173</v>
+        <v>3.337286577263026</v>
       </c>
       <c r="N4" t="n">
-        <v>19.52854045753188</v>
+        <v>19.39584733064986</v>
       </c>
       <c r="O4" t="n">
-        <v>4.419110822046883</v>
+        <v>4.404071676375154</v>
       </c>
       <c r="P4" t="n">
-        <v>316.8319024898054</v>
+        <v>316.8328995435884</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26045,28 +26219,28 @@
         <v>0.09370000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6211594221311781</v>
+        <v>0.6184050601425629</v>
       </c>
       <c r="J5" t="n">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="K5" t="n">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6033736117699604</v>
+        <v>0.6042393590188662</v>
       </c>
       <c r="M5" t="n">
-        <v>2.897782477114975</v>
+        <v>2.895119277245981</v>
       </c>
       <c r="N5" t="n">
-        <v>14.68139356341929</v>
+        <v>14.61134287151635</v>
       </c>
       <c r="O5" t="n">
-        <v>3.831630666363772</v>
+        <v>3.822478629307998</v>
       </c>
       <c r="P5" t="n">
-        <v>321.5484828014742</v>
+        <v>321.5771700239662</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26123,28 +26297,28 @@
         <v>0.09130000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6213517146785096</v>
+        <v>0.6156293772991875</v>
       </c>
       <c r="J6" t="n">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="K6" t="n">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6562390052379581</v>
+        <v>0.6528614834344491</v>
       </c>
       <c r="M6" t="n">
-        <v>2.771317980057909</v>
+        <v>2.786875114195638</v>
       </c>
       <c r="N6" t="n">
-        <v>11.70672437445505</v>
+        <v>11.75549444394628</v>
       </c>
       <c r="O6" t="n">
-        <v>3.421509078528807</v>
+        <v>3.428628653550319</v>
       </c>
       <c r="P6" t="n">
-        <v>326.5960360355617</v>
+        <v>326.6556276278812</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26201,28 +26375,28 @@
         <v>0.09039999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6461493102311788</v>
+        <v>0.6435000579635574</v>
       </c>
       <c r="J7" t="n">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="K7" t="n">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7498137975303564</v>
+        <v>0.75036962694242</v>
       </c>
       <c r="M7" t="n">
-        <v>2.327385536142221</v>
+        <v>2.326705720586095</v>
       </c>
       <c r="N7" t="n">
-        <v>8.063833115957566</v>
+        <v>8.035998241996808</v>
       </c>
       <c r="O7" t="n">
-        <v>2.839688911827767</v>
+        <v>2.834783632307201</v>
       </c>
       <c r="P7" t="n">
-        <v>327.7858027619547</v>
+        <v>327.8133922519748</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26279,28 +26453,28 @@
         <v>0.0853</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6678065891667814</v>
+        <v>0.6611476183905922</v>
       </c>
       <c r="J8" t="n">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="K8" t="n">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6888199295643842</v>
+        <v>0.6844219762101955</v>
       </c>
       <c r="M8" t="n">
-        <v>2.756006118214771</v>
+        <v>2.776436964675786</v>
       </c>
       <c r="N8" t="n">
-        <v>11.66200717619743</v>
+        <v>11.75709845825777</v>
       </c>
       <c r="O8" t="n">
-        <v>3.414968107639869</v>
+        <v>3.428862560421134</v>
       </c>
       <c r="P8" t="n">
-        <v>328.0207060491059</v>
+        <v>328.0900530320225</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26357,28 +26531,28 @@
         <v>0.0963</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6261108799931567</v>
+        <v>0.6192019632189083</v>
       </c>
       <c r="J9" t="n">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="K9" t="n">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="L9" t="n">
-        <v>0.675698216859383</v>
+        <v>0.6702075028794281</v>
       </c>
       <c r="M9" t="n">
-        <v>2.443615353652288</v>
+        <v>2.462972679139653</v>
       </c>
       <c r="N9" t="n">
-        <v>10.89092829956636</v>
+        <v>11.00567308148746</v>
       </c>
       <c r="O9" t="n">
-        <v>3.300140648452178</v>
+        <v>3.317479929326997</v>
       </c>
       <c r="P9" t="n">
-        <v>327.4137544871806</v>
+        <v>327.4857072237493</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26435,28 +26609,28 @@
         <v>0.0804</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6208650215504217</v>
+        <v>0.6144155431452044</v>
       </c>
       <c r="J10" t="n">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="K10" t="n">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="L10" t="n">
-        <v>0.672106370783276</v>
+        <v>0.6673761833288847</v>
       </c>
       <c r="M10" t="n">
-        <v>2.466968303245317</v>
+        <v>2.489723750131827</v>
       </c>
       <c r="N10" t="n">
-        <v>10.88567055810736</v>
+        <v>10.97558049462808</v>
       </c>
       <c r="O10" t="n">
-        <v>3.299343958745035</v>
+        <v>3.312941366011189</v>
       </c>
       <c r="P10" t="n">
-        <v>324.1720508968023</v>
+        <v>324.2392120949735</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -26513,28 +26687,28 @@
         <v>0.08939999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6458623250651183</v>
+        <v>0.6372300365277092</v>
       </c>
       <c r="J11" t="n">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="K11" t="n">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6470939535479698</v>
+        <v>0.6391909813283748</v>
       </c>
       <c r="M11" t="n">
-        <v>2.646823467479838</v>
+        <v>2.673438788587649</v>
       </c>
       <c r="N11" t="n">
-        <v>13.0700781647256</v>
+        <v>13.27132251028717</v>
       </c>
       <c r="O11" t="n">
-        <v>3.615256306920106</v>
+        <v>3.64298263930631</v>
       </c>
       <c r="P11" t="n">
-        <v>321.4953273375843</v>
+        <v>321.585724562522</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -26591,28 +26765,28 @@
         <v>0.08359999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>0.591353191061851</v>
+        <v>0.5804853339703679</v>
       </c>
       <c r="J12" t="n">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="K12" t="n">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="L12" t="n">
-        <v>0.5774270959410448</v>
+        <v>0.5642935227136403</v>
       </c>
       <c r="M12" t="n">
-        <v>2.994091395740163</v>
+        <v>3.035401813829176</v>
       </c>
       <c r="N12" t="n">
-        <v>14.70296420684254</v>
+        <v>15.06421254995831</v>
       </c>
       <c r="O12" t="n">
-        <v>3.834444445658659</v>
+        <v>3.881264297874896</v>
       </c>
       <c r="P12" t="n">
-        <v>321.9311061259671</v>
+        <v>322.0449185241463</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -26669,28 +26843,28 @@
         <v>0.1067</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3422838228858139</v>
+        <v>0.3366950424839283</v>
       </c>
       <c r="J13" t="n">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="K13" t="n">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="L13" t="n">
-        <v>0.324301967240881</v>
+        <v>0.3184087321765885</v>
       </c>
       <c r="M13" t="n">
-        <v>2.902235731126567</v>
+        <v>2.906217907224849</v>
       </c>
       <c r="N13" t="n">
-        <v>14.0243371262102</v>
+        <v>14.05036066057752</v>
       </c>
       <c r="O13" t="n">
-        <v>3.744908159916635</v>
+        <v>3.748381071953267</v>
       </c>
       <c r="P13" t="n">
-        <v>326.0843813331236</v>
+        <v>326.1429098046859</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -26728,7 +26902,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N433"/>
+  <dimension ref="A1:N436"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57887,6 +58061,222 @@
         </is>
       </c>
     </row>
+    <row r="434">
+      <c r="A434" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-07 22:07:26+00:00</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>-42.50543988288092,173.50995996038455</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>-42.50601178459898,173.509472593601</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>-42.50664032757661,173.50918737703498</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>-42.50726302748368,173.50888133097916</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>-42.507891348455566,173.50858342667965</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>-42.50853999073012,173.50837823109723</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>-42.5091775677513,173.50812823368062</t>
+        </is>
+      </c>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>-42.50982019065159,173.50789845107593</t>
+        </is>
+      </c>
+      <c r="J434" t="inlineStr">
+        <is>
+          <t>-42.51046741870683,173.5076904777063</t>
+        </is>
+      </c>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>-42.51111316420248,173.50748623762274</t>
+        </is>
+      </c>
+      <c r="L434" t="inlineStr">
+        <is>
+          <t>-42.51176141902744,173.50729782643637</t>
+        </is>
+      </c>
+      <c r="M434" t="inlineStr">
+        <is>
+          <t>-42.51241595276587,173.507157448807</t>
+        </is>
+      </c>
+      <c r="N434" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:06:47+00:00</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>-42.50543225976369,173.50993275667963</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>-42.50600789325594,173.5094587070864</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>-42.5066375525878,173.50917747426465</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>-42.50726006109845,173.50887074516308</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>-42.507890978461525,173.50858192545235</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>-42.50853996714616,173.50837811362652</t>
+        </is>
+      </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>-42.50917681769709,173.5081240958632</t>
+        </is>
+      </c>
+      <c r="I435" t="inlineStr">
+        <is>
+          <t>-42.50981905632842,173.50789106174432</t>
+        </is>
+      </c>
+      <c r="J435" t="inlineStr">
+        <is>
+          <t>-42.51046740279679,173.50769035789855</t>
+        </is>
+      </c>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>-42.51111305291597,173.50748539893962</t>
+        </is>
+      </c>
+      <c r="L435" t="inlineStr">
+        <is>
+          <t>-42.51176018190799,173.50728835667144</t>
+        </is>
+      </c>
+      <c r="M435" t="inlineStr">
+        <is>
+          <t>-42.512414687228876,173.50714761493091</t>
+        </is>
+      </c>
+      <c r="N435" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-23 22:06:58+00:00</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>-42.505432387347305,173.5099332119717</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>-42.506005915687524,173.50945165000584</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>-42.506635989662676,173.50917189684264</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>-42.5072604757545,173.50887222490076</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>-42.507891319994485,173.50858331120062</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>-42.50853970772273,173.50837682144865</t>
+        </is>
+      </c>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>-42.509176860557325,173.5081243323099</t>
+        </is>
+      </c>
+      <c r="I436" t="inlineStr">
+        <is>
+          <t>-42.50981843428003,173.50788700953032</t>
+        </is>
+      </c>
+      <c r="J436" t="inlineStr">
+        <is>
+          <t>-42.5104683414894,173.507697426555</t>
+        </is>
+      </c>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>-42.511113482163914,173.50748863386025</t>
+        </is>
+      </c>
+      <c r="L436" t="inlineStr">
+        <is>
+          <t>-42.51176032284569,173.5072894355054</t>
+        </is>
+      </c>
+      <c r="M436" t="inlineStr">
+        <is>
+          <t>-42.51241519653045,173.50715157246637</t>
+        </is>
+      </c>
+      <c r="N436" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0396/nzd0396.xlsx
+++ b/data/nzd0396/nzd0396.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N436"/>
+  <dimension ref="A1:N438"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21368,6 +21368,102 @@
         <v>330.94</v>
       </c>
       <c r="N436" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:07:04+00:00</t>
+        </is>
+      </c>
+      <c r="B437" t="n">
+        <v>342.7</v>
+      </c>
+      <c r="C437" t="n">
+        <v>329.9</v>
+      </c>
+      <c r="D437" t="n">
+        <v>333.04</v>
+      </c>
+      <c r="E437" t="n">
+        <v>335.54</v>
+      </c>
+      <c r="F437" t="n">
+        <v>339.34</v>
+      </c>
+      <c r="G437" t="n">
+        <v>343.11</v>
+      </c>
+      <c r="H437" t="n">
+        <v>340.15</v>
+      </c>
+      <c r="I437" t="n">
+        <v>338.56</v>
+      </c>
+      <c r="J437" t="n">
+        <v>336.15</v>
+      </c>
+      <c r="K437" t="n">
+        <v>332.15</v>
+      </c>
+      <c r="L437" t="n">
+        <v>328.98</v>
+      </c>
+      <c r="M437" t="n">
+        <v>330.22</v>
+      </c>
+      <c r="N437" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:06:46+00:00</t>
+        </is>
+      </c>
+      <c r="B438" t="n">
+        <v>342.37</v>
+      </c>
+      <c r="C438" t="n">
+        <v>329.21</v>
+      </c>
+      <c r="D438" t="n">
+        <v>331.85</v>
+      </c>
+      <c r="E438" t="n">
+        <v>334.57</v>
+      </c>
+      <c r="F438" t="n">
+        <v>338.25</v>
+      </c>
+      <c r="G438" t="n">
+        <v>342.68</v>
+      </c>
+      <c r="H438" t="n">
+        <v>339.7</v>
+      </c>
+      <c r="I438" t="n">
+        <v>338.18</v>
+      </c>
+      <c r="J438" t="n">
+        <v>335.93</v>
+      </c>
+      <c r="K438" t="n">
+        <v>331.93</v>
+      </c>
+      <c r="L438" t="n">
+        <v>328.74</v>
+      </c>
+      <c r="M438" t="n">
+        <v>330.41</v>
+      </c>
+      <c r="N438" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -21384,7 +21480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B443"/>
+  <dimension ref="A1:B445"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25817,6 +25913,26 @@
       </c>
       <c r="B443" t="n">
         <v>0.6</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B444" t="n">
+        <v>-0.57</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B445" t="n">
+        <v>0.34</v>
       </c>
     </row>
   </sheetData>
@@ -25985,28 +26101,28 @@
         <v>0.0562</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7734120976944007</v>
+        <v>0.7712962311153796</v>
       </c>
       <c r="J2" t="n">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="K2" t="n">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="L2" t="n">
-        <v>0.415145265059165</v>
+        <v>0.4160181175502998</v>
       </c>
       <c r="M2" t="n">
-        <v>5.656537457741214</v>
+        <v>5.64582614120433</v>
       </c>
       <c r="N2" t="n">
-        <v>49.15755983809073</v>
+        <v>48.95984265536151</v>
       </c>
       <c r="O2" t="n">
-        <v>7.01124524161655</v>
+        <v>6.99713103031246</v>
       </c>
       <c r="P2" t="n">
-        <v>324.2646469576103</v>
+        <v>324.2867370724588</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26063,28 +26179,28 @@
         <v>0.0827</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6412625554209999</v>
+        <v>0.6396303800506339</v>
       </c>
       <c r="J3" t="n">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="K3" t="n">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="L3" t="n">
-        <v>0.460684561924208</v>
+        <v>0.4616706784118129</v>
       </c>
       <c r="M3" t="n">
-        <v>4.161036147352966</v>
+        <v>4.152608616888736</v>
       </c>
       <c r="N3" t="n">
-        <v>27.873142588289</v>
+        <v>27.76181245000117</v>
       </c>
       <c r="O3" t="n">
-        <v>5.27950211556819</v>
+        <v>5.268947945273436</v>
       </c>
       <c r="P3" t="n">
-        <v>314.2503389187501</v>
+        <v>314.2674752312854</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26141,28 +26257,28 @@
         <v>0.0806</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6630531497936767</v>
+        <v>0.66117914888089</v>
       </c>
       <c r="J4" t="n">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="K4" t="n">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5675469943993632</v>
+        <v>0.5682402632821675</v>
       </c>
       <c r="M4" t="n">
-        <v>3.337286577263026</v>
+        <v>3.334712503833567</v>
       </c>
       <c r="N4" t="n">
-        <v>19.39584733064986</v>
+        <v>19.32957666329621</v>
       </c>
       <c r="O4" t="n">
-        <v>4.404071676375154</v>
+        <v>4.396541443372985</v>
       </c>
       <c r="P4" t="n">
-        <v>316.8328995435884</v>
+        <v>316.8525757041762</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26219,28 +26335,28 @@
         <v>0.09370000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6184050601425629</v>
+        <v>0.6157368539751746</v>
       </c>
       <c r="J5" t="n">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="K5" t="n">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6042393590188662</v>
+        <v>0.6037479086339157</v>
       </c>
       <c r="M5" t="n">
-        <v>2.895119277245981</v>
+        <v>2.898602367411836</v>
       </c>
       <c r="N5" t="n">
-        <v>14.61134287151635</v>
+        <v>14.58870325820526</v>
       </c>
       <c r="O5" t="n">
-        <v>3.822478629307998</v>
+        <v>3.81951610262416</v>
       </c>
       <c r="P5" t="n">
-        <v>321.5771700239662</v>
+        <v>321.6050279234006</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26297,28 +26413,28 @@
         <v>0.09130000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6156293772991875</v>
+        <v>0.6118669271772642</v>
       </c>
       <c r="J6" t="n">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="K6" t="n">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6528614834344491</v>
+        <v>0.6505801730834329</v>
       </c>
       <c r="M6" t="n">
-        <v>2.786875114195638</v>
+        <v>2.79686597476411</v>
       </c>
       <c r="N6" t="n">
-        <v>11.75549444394628</v>
+        <v>11.7888419371443</v>
       </c>
       <c r="O6" t="n">
-        <v>3.428628653550319</v>
+        <v>3.433488304500876</v>
       </c>
       <c r="P6" t="n">
-        <v>326.6556276278812</v>
+        <v>326.6949095424783</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26375,28 +26491,28 @@
         <v>0.09039999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6435000579635574</v>
+        <v>0.6416307463405752</v>
       </c>
       <c r="J7" t="n">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="K7" t="n">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="L7" t="n">
-        <v>0.75036962694242</v>
+        <v>0.7505831817738806</v>
       </c>
       <c r="M7" t="n">
-        <v>2.326705720586095</v>
+        <v>2.326843014773661</v>
       </c>
       <c r="N7" t="n">
-        <v>8.035998241996808</v>
+        <v>8.02061564421456</v>
       </c>
       <c r="O7" t="n">
-        <v>2.834783632307201</v>
+        <v>2.832069145380204</v>
       </c>
       <c r="P7" t="n">
-        <v>327.8133922519748</v>
+        <v>327.8329085927744</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26453,28 +26569,28 @@
         <v>0.0853</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6611476183905922</v>
+        <v>0.6560686672352911</v>
       </c>
       <c r="J8" t="n">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="K8" t="n">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6844219762101955</v>
+        <v>0.6802864606827974</v>
       </c>
       <c r="M8" t="n">
-        <v>2.776436964675786</v>
+        <v>2.793861962352123</v>
       </c>
       <c r="N8" t="n">
-        <v>11.75709845825777</v>
+        <v>11.85982445127405</v>
       </c>
       <c r="O8" t="n">
-        <v>3.428862560421134</v>
+        <v>3.44380958406153</v>
       </c>
       <c r="P8" t="n">
-        <v>328.0900530320225</v>
+        <v>328.143077571466</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26531,28 +26647,28 @@
         <v>0.0963</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6192019632189083</v>
+        <v>0.6142774831088211</v>
       </c>
       <c r="J9" t="n">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="K9" t="n">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6702075028794281</v>
+        <v>0.6658437410521025</v>
       </c>
       <c r="M9" t="n">
-        <v>2.462972679139653</v>
+        <v>2.477519464073256</v>
       </c>
       <c r="N9" t="n">
-        <v>11.00567308148746</v>
+        <v>11.1024016973827</v>
       </c>
       <c r="O9" t="n">
-        <v>3.317479929326997</v>
+        <v>3.332026665166817</v>
       </c>
       <c r="P9" t="n">
-        <v>327.4857072237493</v>
+        <v>327.5371189330525</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26609,28 +26725,28 @@
         <v>0.0804</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6144155431452044</v>
+        <v>0.610391273625245</v>
       </c>
       <c r="J10" t="n">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="K10" t="n">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6673761833288847</v>
+        <v>0.6646047261071821</v>
       </c>
       <c r="M10" t="n">
-        <v>2.489723750131827</v>
+        <v>2.503056273448718</v>
       </c>
       <c r="N10" t="n">
-        <v>10.97558049462808</v>
+        <v>11.02352804805917</v>
       </c>
       <c r="O10" t="n">
-        <v>3.312941366011189</v>
+        <v>3.320169882409508</v>
       </c>
       <c r="P10" t="n">
-        <v>324.2392120949735</v>
+        <v>324.2812253769259</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -26687,28 +26803,28 @@
         <v>0.08939999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6372300365277092</v>
+        <v>0.6314781273399036</v>
       </c>
       <c r="J11" t="n">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="K11" t="n">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6391909813283748</v>
+        <v>0.6337817163784272</v>
       </c>
       <c r="M11" t="n">
-        <v>2.673438788587649</v>
+        <v>2.691392056370705</v>
       </c>
       <c r="N11" t="n">
-        <v>13.27132251028717</v>
+        <v>13.40882888017141</v>
       </c>
       <c r="O11" t="n">
-        <v>3.64298263930631</v>
+        <v>3.661806778104411</v>
       </c>
       <c r="P11" t="n">
-        <v>321.585724562522</v>
+        <v>321.6461091255999</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -26765,28 +26881,28 @@
         <v>0.08359999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5804853339703679</v>
+        <v>0.5728898717596561</v>
       </c>
       <c r="J12" t="n">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="K12" t="n">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="L12" t="n">
-        <v>0.5642935227136403</v>
+        <v>0.5545617508647253</v>
       </c>
       <c r="M12" t="n">
-        <v>3.035401813829176</v>
+        <v>3.065628007733815</v>
       </c>
       <c r="N12" t="n">
-        <v>15.06421254995831</v>
+        <v>15.34100424625636</v>
       </c>
       <c r="O12" t="n">
-        <v>3.881264297874896</v>
+        <v>3.916759406225554</v>
       </c>
       <c r="P12" t="n">
-        <v>322.0449185241463</v>
+        <v>322.1246568891381</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -26843,28 +26959,28 @@
         <v>0.1067</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3366950424839283</v>
+        <v>0.3324807273541811</v>
       </c>
       <c r="J13" t="n">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="K13" t="n">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="L13" t="n">
-        <v>0.3184087321765885</v>
+        <v>0.3134129157505424</v>
       </c>
       <c r="M13" t="n">
-        <v>2.906217907224849</v>
+        <v>2.912416059640504</v>
       </c>
       <c r="N13" t="n">
-        <v>14.05036066057752</v>
+        <v>14.09242066890352</v>
       </c>
       <c r="O13" t="n">
-        <v>3.748381071953267</v>
+        <v>3.753987302709417</v>
       </c>
       <c r="P13" t="n">
-        <v>326.1429098046859</v>
+        <v>326.1871516028589</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -26902,7 +27018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N436"/>
+  <dimension ref="A1:N438"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58277,6 +58393,150 @@
         </is>
       </c>
     </row>
+    <row r="437">
+      <c r="A437" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:07:04+00:00</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>-42.505427571064935,173.509916024697</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>-42.506005022591964,173.50944846293737</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>-42.50663331036185,173.50916233554844</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>-42.50725955075251,173.5088689239475</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>-42.507892657665074,173.50858873871485</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>-42.508540061481966,173.50837858350934</t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>-42.50917572476066,173.5081180664723</t>
+        </is>
+      </c>
+      <c r="I437" t="inlineStr">
+        <is>
+          <t>-42.50981865382653,173.50788843972347</t>
+        </is>
+      </c>
+      <c r="J437" t="inlineStr">
+        <is>
+          <t>-42.51046821420908,173.5076964680931</t>
+        </is>
+      </c>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>-42.5111131483044,173.50748611781086</t>
+        </is>
+      </c>
+      <c r="L437" t="inlineStr">
+        <is>
+          <t>-42.511759853053334,173.5072858393922</t>
+        </is>
+      </c>
+      <c r="M437" t="inlineStr">
+        <is>
+          <t>-42.51241408532684,173.50714293784367</t>
+        </is>
+      </c>
+      <c r="N437" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:06:46+00:00</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>-42.505426518499576,173.509912268538</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>-42.50600282174896,173.5094406090904</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>-42.506629514684285,173.50914879038305</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>-42.5072564567796,173.50885788282872</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>-42.50788955540737,173.5085761515013</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>-42.5085390473721,173.5083735322688</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>-42.50917476040474,173.50811274642163</t>
+        </is>
+      </c>
+      <c r="I438" t="inlineStr">
+        <is>
+          <t>-42.50981795859586,173.5078839107785</t>
+        </is>
+      </c>
+      <c r="J438" t="inlineStr">
+        <is>
+          <t>-42.51046786418811,173.50769383232287</t>
+        </is>
+      </c>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>-42.51111279854676,173.50748348194963</t>
+        </is>
+      </c>
+      <c r="L438" t="inlineStr">
+        <is>
+          <t>-42.51175947721934,173.5072829625017</t>
+        </is>
+      </c>
+      <c r="M438" t="inlineStr">
+        <is>
+          <t>-42.51241437856118,173.50714521642462</t>
+        </is>
+      </c>
+      <c r="N438" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0396/nzd0396.xlsx
+++ b/data/nzd0396/nzd0396.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N438"/>
+  <dimension ref="A1:N439"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21464,6 +21464,54 @@
         <v>330.41</v>
       </c>
       <c r="N438" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:06:54+00:00</t>
+        </is>
+      </c>
+      <c r="B439" t="n">
+        <v>341.51</v>
+      </c>
+      <c r="C439" t="n">
+        <v>328.3</v>
+      </c>
+      <c r="D439" t="n">
+        <v>331.68</v>
+      </c>
+      <c r="E439" t="n">
+        <v>334.16</v>
+      </c>
+      <c r="F439" t="n">
+        <v>338.65</v>
+      </c>
+      <c r="G439" t="n">
+        <v>343.62</v>
+      </c>
+      <c r="H439" t="n">
+        <v>339.96</v>
+      </c>
+      <c r="I439" t="n">
+        <v>338.34</v>
+      </c>
+      <c r="J439" t="n">
+        <v>335.02</v>
+      </c>
+      <c r="K439" t="n">
+        <v>330.6</v>
+      </c>
+      <c r="L439" t="n">
+        <v>327.61</v>
+      </c>
+      <c r="M439" t="n">
+        <v>330.29</v>
+      </c>
+      <c r="N439" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -21480,7 +21528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B445"/>
+  <dimension ref="A1:B446"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25933,6 +25981,16 @@
       </c>
       <c r="B445" t="n">
         <v>0.34</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B446" t="n">
+        <v>0.11</v>
       </c>
     </row>
   </sheetData>
@@ -26101,28 +26159,28 @@
         <v>0.0562</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7712962311153796</v>
+        <v>0.7697728090170348</v>
       </c>
       <c r="J2" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="K2" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4160181175502998</v>
+        <v>0.4160914892559424</v>
       </c>
       <c r="M2" t="n">
-        <v>5.64582614120433</v>
+        <v>5.643776341790677</v>
       </c>
       <c r="N2" t="n">
-        <v>48.95984265536151</v>
+        <v>48.87622229060815</v>
       </c>
       <c r="O2" t="n">
-        <v>6.99713103031246</v>
+        <v>6.991153144554062</v>
       </c>
       <c r="P2" t="n">
-        <v>324.2867370724588</v>
+        <v>324.3027127666007</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26179,28 +26237,28 @@
         <v>0.0827</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6396303800506339</v>
+        <v>0.6382501390042572</v>
       </c>
       <c r="J3" t="n">
+        <v>438</v>
+      </c>
+      <c r="K3" t="n">
         <v>437</v>
       </c>
-      <c r="K3" t="n">
-        <v>436</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.4616706784118129</v>
+        <v>0.4615967369751464</v>
       </c>
       <c r="M3" t="n">
-        <v>4.152608616888736</v>
+        <v>4.152032580869037</v>
       </c>
       <c r="N3" t="n">
-        <v>27.76181245000117</v>
+        <v>27.72115389196918</v>
       </c>
       <c r="O3" t="n">
-        <v>5.268947945273436</v>
+        <v>5.265088213123231</v>
       </c>
       <c r="P3" t="n">
-        <v>314.2674752312854</v>
+        <v>314.2820297440544</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26257,28 +26315,28 @@
         <v>0.0806</v>
       </c>
       <c r="I4" t="n">
-        <v>0.66117914888089</v>
+        <v>0.6598914897979117</v>
       </c>
       <c r="J4" t="n">
+        <v>438</v>
+      </c>
+      <c r="K4" t="n">
         <v>437</v>
       </c>
-      <c r="K4" t="n">
-        <v>436</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.5682402632821675</v>
+        <v>0.5682200988979835</v>
       </c>
       <c r="M4" t="n">
-        <v>3.334712503833567</v>
+        <v>3.335805829508731</v>
       </c>
       <c r="N4" t="n">
-        <v>19.32957666329621</v>
+        <v>19.30524870094163</v>
       </c>
       <c r="O4" t="n">
-        <v>4.396541443372985</v>
+        <v>4.393773856372404</v>
       </c>
       <c r="P4" t="n">
-        <v>316.8525757041762</v>
+        <v>316.8661539487982</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26335,28 +26393,28 @@
         <v>0.09370000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6157368539751746</v>
+        <v>0.6140062763969247</v>
       </c>
       <c r="J5" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="K5" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6037479086339157</v>
+        <v>0.6029605373339384</v>
       </c>
       <c r="M5" t="n">
-        <v>2.898602367411836</v>
+        <v>2.902738845448902</v>
       </c>
       <c r="N5" t="n">
-        <v>14.58870325820526</v>
+        <v>14.5917349534777</v>
       </c>
       <c r="O5" t="n">
-        <v>3.81951610262416</v>
+        <v>3.819912951034054</v>
       </c>
       <c r="P5" t="n">
-        <v>321.6050279234006</v>
+        <v>321.6231759981258</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26413,28 +26471,28 @@
         <v>0.09130000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6118669271772642</v>
+        <v>0.6099204291460357</v>
       </c>
       <c r="J6" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="K6" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6505801730834329</v>
+        <v>0.6493422571535319</v>
       </c>
       <c r="M6" t="n">
-        <v>2.79686597476411</v>
+        <v>2.802284434160151</v>
       </c>
       <c r="N6" t="n">
-        <v>11.7888419371443</v>
+        <v>11.80789964072973</v>
       </c>
       <c r="O6" t="n">
-        <v>3.433488304500876</v>
+        <v>3.436262452248042</v>
       </c>
       <c r="P6" t="n">
-        <v>326.6949095424783</v>
+        <v>326.715321913566</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26491,28 +26549,28 @@
         <v>0.09039999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6416307463405752</v>
+        <v>0.6409965313758031</v>
       </c>
       <c r="J7" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="K7" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7505831817738806</v>
+        <v>0.7510032175134295</v>
       </c>
       <c r="M7" t="n">
-        <v>2.326843014773661</v>
+        <v>2.325153447678611</v>
       </c>
       <c r="N7" t="n">
-        <v>8.02061564421456</v>
+        <v>8.007184262334844</v>
       </c>
       <c r="O7" t="n">
-        <v>2.832069145380204</v>
+        <v>2.829696849900152</v>
       </c>
       <c r="P7" t="n">
-        <v>327.8329085927744</v>
+        <v>327.8395594246801</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26569,28 +26627,28 @@
         <v>0.0853</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6560686672352911</v>
+        <v>0.6535501934691772</v>
       </c>
       <c r="J8" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="K8" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6802864606827974</v>
+        <v>0.678251038467347</v>
       </c>
       <c r="M8" t="n">
-        <v>2.793861962352123</v>
+        <v>2.802506409159452</v>
       </c>
       <c r="N8" t="n">
-        <v>11.85982445127405</v>
+        <v>11.90970784005277</v>
       </c>
       <c r="O8" t="n">
-        <v>3.44380958406153</v>
+        <v>3.451044456400521</v>
       </c>
       <c r="P8" t="n">
-        <v>328.143077571466</v>
+        <v>328.1694880893622</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26647,28 +26705,28 @@
         <v>0.0963</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6142774831088211</v>
+        <v>0.6118043946425509</v>
       </c>
       <c r="J9" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="K9" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6658437410521025</v>
+        <v>0.6636345218792198</v>
       </c>
       <c r="M9" t="n">
-        <v>2.477519464073256</v>
+        <v>2.484979522862192</v>
       </c>
       <c r="N9" t="n">
-        <v>11.1024016973827</v>
+        <v>11.15126554783203</v>
       </c>
       <c r="O9" t="n">
-        <v>3.332026665166817</v>
+        <v>3.339351066873926</v>
       </c>
       <c r="P9" t="n">
-        <v>327.5371189330525</v>
+        <v>327.5630535082211</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26725,28 +26783,28 @@
         <v>0.0804</v>
       </c>
       <c r="I10" t="n">
-        <v>0.610391273625245</v>
+        <v>0.6079351156313679</v>
       </c>
       <c r="J10" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="K10" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6646047261071821</v>
+        <v>0.6624022178645319</v>
       </c>
       <c r="M10" t="n">
-        <v>2.503056273448718</v>
+        <v>2.512345038691081</v>
       </c>
       <c r="N10" t="n">
-        <v>11.02352804805917</v>
+        <v>11.07155936287147</v>
       </c>
       <c r="O10" t="n">
-        <v>3.320169882409508</v>
+        <v>3.327395282029393</v>
       </c>
       <c r="P10" t="n">
-        <v>324.2812253769259</v>
+        <v>324.306982407047</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -26803,28 +26861,28 @@
         <v>0.08939999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6314781273399036</v>
+        <v>0.6279858358619966</v>
       </c>
       <c r="J11" t="n">
+        <v>438</v>
+      </c>
+      <c r="K11" t="n">
         <v>437</v>
       </c>
-      <c r="K11" t="n">
-        <v>436</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.6337817163784272</v>
+        <v>0.6297973110715845</v>
       </c>
       <c r="M11" t="n">
-        <v>2.691392056370705</v>
+        <v>2.703898766233512</v>
       </c>
       <c r="N11" t="n">
-        <v>13.40882888017141</v>
+        <v>13.52455480514128</v>
       </c>
       <c r="O11" t="n">
-        <v>3.661806778104411</v>
+        <v>3.677574581859799</v>
       </c>
       <c r="P11" t="n">
-        <v>321.6461091255999</v>
+        <v>321.6829350126735</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -26881,28 +26939,28 @@
         <v>0.08359999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5728898717596561</v>
+        <v>0.5685717442613437</v>
       </c>
       <c r="J12" t="n">
+        <v>438</v>
+      </c>
+      <c r="K12" t="n">
         <v>437</v>
       </c>
-      <c r="K12" t="n">
-        <v>436</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.5545617508647253</v>
+        <v>0.5484270068367163</v>
       </c>
       <c r="M12" t="n">
-        <v>3.065628007733815</v>
+        <v>3.084007965318173</v>
       </c>
       <c r="N12" t="n">
-        <v>15.34100424625636</v>
+        <v>15.52974012694176</v>
       </c>
       <c r="O12" t="n">
-        <v>3.916759406225554</v>
+        <v>3.94077912689125</v>
       </c>
       <c r="P12" t="n">
-        <v>322.1246568891381</v>
+        <v>322.1701911398237</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -26959,28 +27017,28 @@
         <v>0.1067</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3324807273541811</v>
+        <v>0.3303737586432844</v>
       </c>
       <c r="J13" t="n">
+        <v>438</v>
+      </c>
+      <c r="K13" t="n">
         <v>437</v>
       </c>
-      <c r="K13" t="n">
-        <v>436</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.3134129157505424</v>
+        <v>0.3109115839002953</v>
       </c>
       <c r="M13" t="n">
-        <v>2.912416059640504</v>
+        <v>2.915594131648561</v>
       </c>
       <c r="N13" t="n">
-        <v>14.09242066890352</v>
+        <v>14.11346495518309</v>
       </c>
       <c r="O13" t="n">
-        <v>3.753987302709417</v>
+        <v>3.756789181626125</v>
       </c>
       <c r="P13" t="n">
-        <v>326.1871516028589</v>
+        <v>326.2093693908947</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -27018,7 +27076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N438"/>
+  <dimension ref="A1:N439"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58537,6 +58595,78 @@
         </is>
       </c>
     </row>
+    <row r="439">
+      <c r="A439" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:06:54+00:00</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>-42.505423775449856,173.5099024797605</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>-42.505999919187055,173.50943025111917</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>-42.50662897244449,173.50914685535955</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>-42.507255149017546,173.50885321596445</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>-42.50789069385072,173.50858077066212</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>-42.508541264263144,173.5083845745158</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>-42.5091753175882,173.50811582022865</t>
+        </is>
+      </c>
+      <c r="I439" t="inlineStr">
+        <is>
+          <t>-42.5098182513246,173.5078858177027</t>
+        </is>
+      </c>
+      <c r="J439" t="inlineStr">
+        <is>
+          <t>-42.510466416373575,173.5076829298191</t>
+        </is>
+      </c>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>-42.511110684101574,173.50746754697113</t>
+        </is>
+      </c>
+      <c r="L439" t="inlineStr">
+        <is>
+          <t>-42.51175770766674,173.50726941714268</t>
+        </is>
+      </c>
+      <c r="M439" t="inlineStr">
+        <is>
+          <t>-42.51241419336054,173.50714377732086</t>
+        </is>
+      </c>
+      <c r="N439" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
